--- a/CROWDED VERSION ANSWERS.xlsx
+++ b/CROWDED VERSION ANSWERS.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="47">
   <si>
     <t>P01</t>
   </si>
@@ -151,6 +151,15 @@
   </si>
   <si>
     <t>Left</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Male</t>
   </si>
 </sst>
 </file>
@@ -223,7 +232,229 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -244,204 +475,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
           <bgColor rgb="FFF8F9FA"/>
@@ -483,10 +516,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Form Yanıtları 1-style" pivot="0" count="4">
-      <tableStyleElement type="wholeTable" size="0" dxfId="21"/>
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="secondRowStripe" dxfId="18"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="22"/>
+      <tableStyleElement type="headerRow" dxfId="21"/>
+      <tableStyleElement type="firstRowStripe" dxfId="20"/>
+      <tableStyleElement type="secondRowStripe" dxfId="19"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -505,13 +538,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:P21" headerRowDxfId="0" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:Q21" headerRowDxfId="18" dataDxfId="17">
   <sortState ref="A2:Q21">
     <sortCondition ref="A5"/>
   </sortState>
-  <tableColumns count="16">
+  <tableColumns count="17">
     <tableColumn id="3" name="Participant  " dataDxfId="16"/>
     <tableColumn id="4" name="Age " dataDxfId="15"/>
+    <tableColumn id="1" name="Gender" dataDxfId="0"/>
     <tableColumn id="5" name="Department" dataDxfId="14"/>
     <tableColumn id="8" name="Which hand is your dominant hand?" dataDxfId="13"/>
     <tableColumn id="9" name="This image is visually appealing." dataDxfId="12"/>
@@ -732,29 +766,29 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" customWidth="1"/>
-    <col min="3" max="3" width="48.5546875" customWidth="1"/>
-    <col min="4" max="4" width="37.44140625" customWidth="1"/>
-    <col min="5" max="5" width="28.44140625" customWidth="1"/>
-    <col min="6" max="6" width="37.6640625" customWidth="1"/>
-    <col min="7" max="7" width="34.6640625" customWidth="1"/>
-    <col min="8" max="8" width="28.44140625" customWidth="1"/>
-    <col min="9" max="9" width="37.6640625" customWidth="1"/>
-    <col min="10" max="10" width="34.6640625" customWidth="1"/>
-    <col min="11" max="11" width="28.44140625" customWidth="1"/>
-    <col min="12" max="12" width="37.6640625" customWidth="1"/>
-    <col min="13" max="13" width="34.6640625" customWidth="1"/>
-    <col min="14" max="14" width="28.44140625" customWidth="1"/>
-    <col min="15" max="15" width="37.6640625" customWidth="1"/>
-    <col min="16" max="16" width="48.33203125" customWidth="1"/>
-    <col min="17" max="22" width="18.88671875" customWidth="1"/>
+    <col min="2" max="3" width="18.88671875" customWidth="1"/>
+    <col min="4" max="4" width="48.5546875" customWidth="1"/>
+    <col min="5" max="5" width="37.44140625" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" customWidth="1"/>
+    <col min="7" max="7" width="37.6640625" customWidth="1"/>
+    <col min="8" max="8" width="34.6640625" customWidth="1"/>
+    <col min="9" max="9" width="28.44140625" customWidth="1"/>
+    <col min="10" max="10" width="37.6640625" customWidth="1"/>
+    <col min="11" max="11" width="34.6640625" customWidth="1"/>
+    <col min="12" max="12" width="28.44140625" customWidth="1"/>
+    <col min="13" max="13" width="37.6640625" customWidth="1"/>
+    <col min="14" max="14" width="34.6640625" customWidth="1"/>
+    <col min="15" max="15" width="28.44140625" customWidth="1"/>
+    <col min="16" max="16" width="37.6640625" customWidth="1"/>
+    <col min="17" max="17" width="48.33203125" customWidth="1"/>
+    <col min="18" max="23" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -762,99 +796,105 @@
         <v>21</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2">
         <v>19</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="2">
-        <v>4</v>
-      </c>
       <c r="F2" s="2">
         <v>4</v>
       </c>
       <c r="G2" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I2" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N2" s="2">
         <v>2</v>
       </c>
       <c r="O2" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P2" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -862,49 +902,52 @@
         <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="2">
-        <v>4</v>
-      </c>
       <c r="F3" s="2">
         <v>4</v>
       </c>
       <c r="G3" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" s="2">
         <v>4</v>
       </c>
       <c r="J3" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N3" s="2">
         <v>4</v>
       </c>
       <c r="O3" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P3" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -912,19 +955,19 @@
         <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="2">
-        <v>3</v>
-      </c>
       <c r="F4" s="2">
         <v>3</v>
       </c>
       <c r="G4" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2">
         <v>4</v>
@@ -936,25 +979,28 @@
         <v>4</v>
       </c>
       <c r="K4" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -962,49 +1008,52 @@
         <v>41</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="2">
-        <v>3</v>
-      </c>
       <c r="F5" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="2">
         <v>5</v>
       </c>
       <c r="H5" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5" s="2">
         <v>3</v>
       </c>
       <c r="J5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" s="2">
         <v>4</v>
       </c>
       <c r="P5" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1012,49 +1061,52 @@
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="2">
-        <v>3</v>
-      </c>
       <c r="F6" s="2">
         <v>3</v>
       </c>
       <c r="G6" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="2">
         <v>4</v>
       </c>
       <c r="J6" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O6" s="2">
         <v>4</v>
       </c>
       <c r="P6" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1062,49 +1114,52 @@
         <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="2">
-        <v>3</v>
-      </c>
       <c r="F7" s="2">
         <v>3</v>
       </c>
       <c r="G7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2">
         <v>3</v>
       </c>
       <c r="K7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7" s="2">
         <v>3</v>
       </c>
       <c r="N7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O7" s="2">
         <v>4</v>
       </c>
       <c r="P7" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,16 +1167,16 @@
         <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="2">
-        <v>3</v>
-      </c>
       <c r="F8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="2">
         <v>4</v>
@@ -1136,25 +1191,28 @@
         <v>4</v>
       </c>
       <c r="K8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8" s="2">
         <v>4</v>
       </c>
       <c r="N8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P8" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q8" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -1162,16 +1220,16 @@
         <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="2">
-        <v>2</v>
-      </c>
       <c r="F9" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2">
         <v>4</v>
@@ -1180,7 +1238,7 @@
         <v>4</v>
       </c>
       <c r="I9" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" s="2">
         <v>5</v>
@@ -1192,19 +1250,22 @@
         <v>5</v>
       </c>
       <c r="M9" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9" s="2">
         <v>4</v>
       </c>
       <c r="O9" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q9" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1212,31 +1273,31 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="2">
-        <v>4</v>
-      </c>
       <c r="F10" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2">
         <v>4</v>
       </c>
       <c r="I10" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10" s="2">
         <v>5</v>
@@ -1245,16 +1306,19 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" s="2">
         <v>4</v>
       </c>
       <c r="P10" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,49 +1326,52 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="2">
-        <v>4</v>
-      </c>
       <c r="F11" s="2">
         <v>4</v>
       </c>
       <c r="G11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2">
+        <v>5</v>
+      </c>
+      <c r="K11" s="2">
         <v>1</v>
       </c>
-      <c r="K11" s="2">
-        <v>5</v>
-      </c>
       <c r="L11" s="2">
         <v>5</v>
       </c>
       <c r="M11" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O11" s="2">
         <v>2</v>
       </c>
       <c r="P11" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1312,14 +1379,14 @@
         <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="2">
-        <v>2</v>
-      </c>
       <c r="F12" s="2">
         <v>2</v>
       </c>
@@ -1336,7 +1403,7 @@
         <v>2</v>
       </c>
       <c r="K12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2">
         <v>3</v>
@@ -1345,7 +1412,7 @@
         <v>3</v>
       </c>
       <c r="N12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12" s="2">
         <v>2</v>
@@ -1353,8 +1420,11 @@
       <c r="P12" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -1362,49 +1432,52 @@
         <v>27</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="2">
-        <v>5</v>
-      </c>
       <c r="F13" s="2">
         <v>5</v>
       </c>
       <c r="G13" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K13" s="2">
         <v>4</v>
       </c>
       <c r="L13" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O13" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P13" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q13" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -1412,25 +1485,25 @@
         <v>19</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="2">
-        <v>3</v>
-      </c>
       <c r="F14" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="2">
         <v>4</v>
       </c>
       <c r="H14" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I14" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="2">
         <v>4</v>
@@ -1445,7 +1518,7 @@
         <v>4</v>
       </c>
       <c r="N14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" s="2">
         <v>3</v>
@@ -1453,8 +1526,11 @@
       <c r="P14" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q14" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1462,19 +1538,19 @@
         <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="2">
-        <v>3</v>
-      </c>
       <c r="F15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="2">
         <v>5</v>
@@ -1489,13 +1565,13 @@
         <v>5</v>
       </c>
       <c r="L15" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N15" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15" s="2">
         <v>4</v>
@@ -1503,8 +1579,11 @@
       <c r="P15" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q15" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,25 +1591,25 @@
         <v>21</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="2">
-        <v>3</v>
-      </c>
       <c r="F16" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="2">
         <v>5</v>
       </c>
       <c r="H16" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J16" s="2">
         <v>5</v>
@@ -1553,8 +1632,11 @@
       <c r="P16" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q16" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1562,19 +1644,19 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="2">
-        <v>4</v>
-      </c>
       <c r="F17" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="2">
         <v>4</v>
@@ -1589,10 +1671,10 @@
         <v>4</v>
       </c>
       <c r="L17" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17" s="2">
         <v>4</v>
@@ -1603,8 +1685,11 @@
       <c r="P17" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q17" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -1612,14 +1697,14 @@
         <v>24</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="2">
-        <v>3</v>
-      </c>
       <c r="F18" s="2">
         <v>3</v>
       </c>
@@ -1627,7 +1712,7 @@
         <v>3</v>
       </c>
       <c r="H18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="2">
         <v>2</v>
@@ -1636,7 +1721,7 @@
         <v>2</v>
       </c>
       <c r="K18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2">
         <v>4</v>
@@ -1645,7 +1730,7 @@
         <v>4</v>
       </c>
       <c r="N18" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O18" s="2">
         <v>2</v>
@@ -1653,8 +1738,11 @@
       <c r="P18" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q18" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1662,49 +1750,52 @@
         <v>43</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="2">
-        <v>2</v>
-      </c>
       <c r="F19" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2">
         <v>4</v>
       </c>
       <c r="H19" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2">
         <v>4</v>
       </c>
       <c r="K19" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L19" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2">
         <v>4</v>
       </c>
       <c r="N19" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O19" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P19" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q19" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -1712,49 +1803,52 @@
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="2">
-        <v>5</v>
-      </c>
       <c r="F20" s="2">
         <v>5</v>
       </c>
       <c r="G20" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K20" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M20" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2">
         <v>4</v>
       </c>
       <c r="P20" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -1762,25 +1856,25 @@
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="2">
-        <v>3</v>
-      </c>
       <c r="F21" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="2">
         <v>4</v>
       </c>
       <c r="H21" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" s="2">
         <v>4</v>
@@ -1789,18 +1883,21 @@
         <v>4</v>
       </c>
       <c r="L21" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M21" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N21" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21" s="2">
         <v>3</v>
       </c>
       <c r="P21" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="2">
         <v>3</v>
       </c>
     </row>
